--- a/Results_experiment/exp_1/preds_1111122222333222.xlsx
+++ b/Results_experiment/exp_1/preds_1111122222333222.xlsx
@@ -660,7 +660,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D2">
-        <v>-0.1776348948478699</v>
+        <v>0.3786974847316742</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -674,7 +674,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D3">
-        <v>2.046990633010864</v>
+        <v>3.555279493331909</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>-0.6472005844116211</v>
+        <v>-0.9984170794487</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -702,7 +702,7 @@
         <v>-8.5</v>
       </c>
       <c r="D5">
-        <v>-6.599318504333496</v>
+        <v>-8.084205627441406</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -716,7 +716,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D6">
-        <v>11.25468254089355</v>
+        <v>8.988624572753906</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -730,7 +730,7 @@
         <v>-10</v>
       </c>
       <c r="D7">
-        <v>-3.483783960342407</v>
+        <v>-3.307106256484985</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -744,7 +744,7 @@
         <v>-9.5</v>
       </c>
       <c r="D8">
-        <v>-5.868825435638428</v>
+        <v>-5.191073417663574</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -758,7 +758,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D9">
-        <v>-1.521874666213989</v>
+        <v>-1.253057718276978</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -772,7 +772,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D10">
-        <v>-3.230557918548584</v>
+        <v>-4.39494800567627</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -786,7 +786,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D11">
-        <v>4.681252002716064</v>
+        <v>6.22327709197998</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -800,7 +800,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>18.46327209472656</v>
+        <v>15.56738185882568</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -814,7 +814,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D13">
-        <v>-1.439634799957275</v>
+        <v>-0.4595375657081604</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -828,7 +828,7 @@
         <v>-0.5</v>
       </c>
       <c r="D14">
-        <v>-0.1889752596616745</v>
+        <v>0.1456042528152466</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -842,7 +842,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D15">
-        <v>-0.4778684377670288</v>
+        <v>0.200764000415802</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -856,7 +856,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D16">
-        <v>1.206305027008057</v>
+        <v>0.3955212235450745</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -870,7 +870,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D17">
-        <v>-3.776124238967896</v>
+        <v>-4.995820045471191</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -884,7 +884,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D18">
-        <v>2.626311540603638</v>
+        <v>4.137045383453369</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -898,7 +898,7 @@
         <v>25.79999923706055</v>
       </c>
       <c r="D19">
-        <v>12.27105045318604</v>
+        <v>18.08382987976074</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -912,7 +912,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D20">
-        <v>-2.945942401885986</v>
+        <v>-3.219603538513184</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -926,7 +926,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D21">
-        <v>-1.421983003616333</v>
+        <v>-0.7436558604240417</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -940,7 +940,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D22">
-        <v>20.32762908935547</v>
+        <v>14.62702751159668</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -954,7 +954,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D23">
-        <v>-0.1776348948478699</v>
+        <v>1.276334285736084</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -968,7 +968,7 @@
         <v>-13.89999961853027</v>
       </c>
       <c r="D24">
-        <v>-7.352584362030029</v>
+        <v>-8.011333465576172</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -982,7 +982,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D25">
-        <v>-0.1776348948478699</v>
+        <v>0.3325046896934509</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -996,7 +996,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D26">
-        <v>1.084922790527344</v>
+        <v>0.5249322652816772</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1010,7 +1010,7 @@
         <v>-4.5</v>
       </c>
       <c r="D27">
-        <v>-0.9718334674835205</v>
+        <v>-2.799683094024658</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1024,7 +1024,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D28">
-        <v>1.05209755897522</v>
+        <v>1.500735521316528</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1038,7 +1038,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D29">
-        <v>-0.154051348567009</v>
+        <v>0.3955212235450745</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1052,7 +1052,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D30">
-        <v>-1.908424854278564</v>
+        <v>-1.781150341033936</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1066,7 +1066,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D31">
-        <v>-14.19463920593262</v>
+        <v>-17.64490699768066</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1080,7 +1080,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D32">
-        <v>-0.1747464835643768</v>
+        <v>0.4235751330852509</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1094,7 +1094,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D33">
-        <v>-2.329030275344849</v>
+        <v>-1.452662229537964</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1108,7 +1108,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D34">
-        <v>0.5727971196174622</v>
+        <v>0.6181226968765259</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1122,7 +1122,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D35">
-        <v>6.552539825439453</v>
+        <v>7.736131191253662</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1136,7 +1136,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D36">
-        <v>-6.865081787109375</v>
+        <v>-6.515765190124512</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1150,7 +1150,7 @@
         <v>-21</v>
       </c>
       <c r="D37">
-        <v>-12.82907390594482</v>
+        <v>-15.43860244750977</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1164,7 +1164,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D38">
-        <v>2.767668962478638</v>
+        <v>2.772417068481445</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1178,7 +1178,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D39">
-        <v>-3.244824647903442</v>
+        <v>-2.958223819732666</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1192,7 +1192,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D40">
-        <v>4.611766338348389</v>
+        <v>3.780303001403809</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1206,7 +1206,7 @@
         <v>-15.69999980926514</v>
       </c>
       <c r="D41">
-        <v>-8.447660446166992</v>
+        <v>-8.75584602355957</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1220,7 +1220,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>-1.160665273666382</v>
+        <v>0.9920105934143066</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1234,7 +1234,7 @@
         <v>-9.5</v>
       </c>
       <c r="D43">
-        <v>-7.413089275360107</v>
+        <v>-7.717448234558105</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1248,7 +1248,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D44">
-        <v>6.352022647857666</v>
+        <v>5.159674167633057</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1262,7 +1262,7 @@
         <v>-15.10000038146973</v>
       </c>
       <c r="D45">
-        <v>-9.075597763061523</v>
+        <v>-9.513238906860352</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1276,7 +1276,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>3.644485712051392</v>
+        <v>3.025701761245728</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1290,7 +1290,7 @@
         <v>10.5</v>
       </c>
       <c r="D47">
-        <v>4.266592979431152</v>
+        <v>5.713063716888428</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1304,7 +1304,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D48">
-        <v>-2.239952325820923</v>
+        <v>-1.482347965240479</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1318,7 +1318,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D49">
-        <v>-3.578892946243286</v>
+        <v>-3.21675443649292</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1332,7 +1332,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D50">
-        <v>0.3222466707229614</v>
+        <v>0.4827180206775665</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1346,7 +1346,7 @@
         <v>3</v>
       </c>
       <c r="D51">
-        <v>-0.1936542242765427</v>
+        <v>0.6010173559188843</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1360,7 +1360,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D52">
-        <v>1.895407438278198</v>
+        <v>2.298486232757568</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1374,7 +1374,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D53">
-        <v>11.94193649291992</v>
+        <v>10.01392269134521</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1388,7 +1388,7 @@
         <v>-28.20000076293945</v>
       </c>
       <c r="D54">
-        <v>-15.04450988769531</v>
+        <v>-22.71651458740234</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1402,7 +1402,7 @@
         <v>-15.19999980926514</v>
       </c>
       <c r="D55">
-        <v>-6.529717922210693</v>
+        <v>-5.684968948364258</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1416,7 +1416,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D56">
-        <v>-3.226808786392212</v>
+        <v>-4.368441581726074</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1430,7 +1430,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D57">
-        <v>2.368125677108765</v>
+        <v>2.962822198867798</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1444,7 +1444,7 @@
         <v>-8.5</v>
       </c>
       <c r="D58">
-        <v>-9.187207221984863</v>
+        <v>-8.341474533081055</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1458,7 +1458,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D59">
-        <v>-6.532980918884277</v>
+        <v>-8.583881378173828</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1472,7 +1472,7 @@
         <v>-7.5</v>
       </c>
       <c r="D60">
-        <v>-0.9720149636268616</v>
+        <v>-1.891304731369019</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1486,7 +1486,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D61">
-        <v>-4.035961151123047</v>
+        <v>-4.770584106445312</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1500,7 +1500,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D62">
-        <v>4.277594089508057</v>
+        <v>3.477999210357666</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1514,7 +1514,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D63">
-        <v>2.469379186630249</v>
+        <v>3.205608367919922</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1528,7 +1528,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D64">
-        <v>-0.2068317234516144</v>
+        <v>0.3417330384254456</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1542,7 +1542,7 @@
         <v>-26.70000076293945</v>
       </c>
       <c r="D65">
-        <v>-15.86803531646729</v>
+        <v>-17.4908504486084</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1556,7 +1556,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D66">
-        <v>-0.2329921573400497</v>
+        <v>-0.1982691884040833</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1570,7 +1570,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D67">
-        <v>15.306715965271</v>
+        <v>12.56975746154785</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1584,7 +1584,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D68">
-        <v>3.713806629180908</v>
+        <v>3.421773195266724</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1598,7 +1598,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D69">
-        <v>-0.952250599861145</v>
+        <v>-2.752028465270996</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1612,7 +1612,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D70">
-        <v>4.275431156158447</v>
+        <v>4.391022682189941</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1626,7 +1626,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D71">
-        <v>3.923996210098267</v>
+        <v>3.739126205444336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1640,7 +1640,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D72">
-        <v>-0.1773820221424103</v>
+        <v>2.0843346118927</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1654,7 +1654,7 @@
         <v>3.5</v>
       </c>
       <c r="D73">
-        <v>2.075840711593628</v>
+        <v>2.906792640686035</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1668,7 +1668,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D74">
-        <v>1.962214946746826</v>
+        <v>-0.8623512387275696</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1682,7 +1682,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D75">
-        <v>4.740609169006348</v>
+        <v>6.708909511566162</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1696,7 +1696,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D76">
-        <v>2.147822618484497</v>
+        <v>2.114248275756836</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1710,7 +1710,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D77">
-        <v>2.192601919174194</v>
+        <v>1.524130821228027</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1724,7 +1724,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D78">
-        <v>-0.4462684392929077</v>
+        <v>-1.878838777542114</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1738,7 +1738,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D79">
-        <v>2.881569385528564</v>
+        <v>4.03185510635376</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1752,7 +1752,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D80">
-        <v>-3.090407609939575</v>
+        <v>-3.608112335205078</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="D81">
-        <v>2.306308031082153</v>
+        <v>2.779833793640137</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1780,7 +1780,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D82">
-        <v>2.695399761199951</v>
+        <v>3.965052604675293</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>-1.700158596038818</v>
+        <v>-1.19847583770752</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1808,7 +1808,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D84">
-        <v>-4.599751949310303</v>
+        <v>-5.867415904998779</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1822,7 +1822,7 @@
         <v>-12.89999961853027</v>
       </c>
       <c r="D85">
-        <v>-10.82764720916748</v>
+        <v>-9.227842330932617</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1836,7 +1836,7 @@
         <v>-2.5</v>
       </c>
       <c r="D86">
-        <v>-3.817329168319702</v>
+        <v>-2.607088565826416</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1850,7 +1850,7 @@
         <v>-0.5</v>
       </c>
       <c r="D87">
-        <v>-0.5847721099853516</v>
+        <v>0.1530691683292389</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1864,7 +1864,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D88">
-        <v>2.503977060317993</v>
+        <v>2.846167087554932</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1878,7 +1878,7 @@
         <v>-1</v>
       </c>
       <c r="D89">
-        <v>-0.6160670518875122</v>
+        <v>0.2847608327865601</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1892,7 +1892,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D90">
-        <v>-3.842632293701172</v>
+        <v>-3.387560606002808</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1906,7 +1906,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D91">
-        <v>2.56679630279541</v>
+        <v>2.90439510345459</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1920,7 +1920,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D92">
-        <v>-1.924879550933838</v>
+        <v>-3.362320899963379</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1934,7 +1934,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D93">
-        <v>3.0087730884552</v>
+        <v>3.511948108673096</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1948,7 +1948,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>-0.1776348948478699</v>
+        <v>0.3183757662773132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1962,7 +1962,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D95">
-        <v>1.179462671279907</v>
+        <v>1.877760648727417</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1976,7 +1976,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D96">
-        <v>-0.1032046526670456</v>
+        <v>0.5694968700408936</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1990,7 +1990,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D97">
-        <v>6.211482524871826</v>
+        <v>6.449826240539551</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2004,7 +2004,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D98">
-        <v>-8.220130920410156</v>
+        <v>-8.159624099731445</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2018,7 +2018,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D99">
-        <v>3.13732647895813</v>
+        <v>3.273006916046143</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2032,7 +2032,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D100">
-        <v>-2.361190319061279</v>
+        <v>-1.225661516189575</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2046,7 +2046,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D101">
-        <v>-15.52297782897949</v>
+        <v>-17.60771560668945</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2060,7 +2060,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D102">
-        <v>2.212682008743286</v>
+        <v>1.547162055969238</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2074,7 +2074,7 @@
         <v>-12.5</v>
       </c>
       <c r="D103">
-        <v>-8.242362976074219</v>
+        <v>-8.500652313232422</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2088,7 +2088,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D104">
-        <v>5.45698881149292</v>
+        <v>6.345073223114014</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2102,7 +2102,7 @@
         <v>17.60000038146973</v>
       </c>
       <c r="D105">
-        <v>14.48112869262695</v>
+        <v>16.18110656738281</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2116,7 +2116,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>-2.117486238479614</v>
+        <v>5.83731746673584</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2130,7 +2130,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D107">
-        <v>-0.1745652258396149</v>
+        <v>0.8962966203689575</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2144,7 +2144,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>2.641370058059692</v>
+        <v>2.449795007705688</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2158,7 +2158,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D109">
-        <v>6.492880344390869</v>
+        <v>4.053143501281738</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2172,7 +2172,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D110">
-        <v>-1.036267757415771</v>
+        <v>-0.693267285823822</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2186,7 +2186,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D111">
-        <v>6.553917407989502</v>
+        <v>7.373356819152832</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2200,7 +2200,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D112">
-        <v>-0.2992641925811768</v>
+        <v>0.3276488780975342</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2214,7 +2214,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D113">
-        <v>-1.104307651519775</v>
+        <v>0.2338614463806152</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2228,7 +2228,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D114">
-        <v>-6.959388256072998</v>
+        <v>-7.215065956115723</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2242,7 +2242,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D115">
-        <v>8.979543685913086</v>
+        <v>7.921881198883057</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2256,7 +2256,7 @@
         <v>39.70000076293945</v>
       </c>
       <c r="D116">
-        <v>2.269197702407837</v>
+        <v>1.512554407119751</v>
       </c>
     </row>
   </sheetData>
